--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487906_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487906_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>W. CABRAL BUERIBERI</t>
+          <t>J. FRANCH DE PABLO</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.4381</v>
+        <v>3.7095</v>
       </c>
       <c r="E2" t="n">
-        <v>1.6043</v>
+        <v>5.272</v>
       </c>
       <c r="F2" t="n">
-        <v>1.8338</v>
+        <v>-1.5625</v>
       </c>
       <c r="G2" t="n">
-        <v>2.4614</v>
+        <v>3.2016</v>
       </c>
       <c r="H2" t="n">
-        <v>-1.1023</v>
+        <v>0.7784</v>
       </c>
       <c r="I2" t="n">
-        <v>3.5637</v>
+        <v>2.4231</v>
       </c>
       <c r="J2" t="n">
-        <v>0.9307</v>
+        <v>3.316</v>
       </c>
       <c r="K2" t="n">
-        <v>-1.9512</v>
+        <v>0.648</v>
       </c>
       <c r="L2" t="n">
-        <v>2.882</v>
+        <v>2.668</v>
       </c>
       <c r="M2" t="n">
-        <v>1.5307</v>
+        <v>-0.1145</v>
       </c>
       <c r="N2" t="n">
-        <v>0.849</v>
+        <v>0.1304</v>
       </c>
       <c r="O2" t="n">
-        <v>0.6817</v>
+        <v>-0.2449</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.4162</v>
+        <v>1.0406</v>
       </c>
       <c r="Q2" t="n">
-        <v>-2.0812</v>
+        <v>-1.0406</v>
       </c>
       <c r="R2" t="n">
-        <v>1.6649</v>
+        <v>2.0812</v>
       </c>
       <c r="S2" t="n">
-        <v>0.9330000000000001</v>
+        <v>-0.5327</v>
       </c>
       <c r="T2" t="n">
-        <v>1.1273</v>
+        <v>0.4315</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.1943</v>
+        <v>-0.9641999999999999</v>
       </c>
       <c r="V2" t="n">
-        <v>0.4599</v>
+        <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>1.6275</v>
+        <v>2.565</v>
       </c>
       <c r="X2" t="n">
-        <v>-1.1675</v>
+        <v>-2.565</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J. FRANCH DE PABLO</t>
+          <t>W. CABRAL BUERIBERI</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.2269</v>
+        <v>2.8524</v>
       </c>
       <c r="E3" t="n">
-        <v>4.2004</v>
+        <v>1.2828</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.9736</v>
+        <v>1.5695</v>
       </c>
       <c r="G3" t="n">
-        <v>3.2016</v>
+        <v>2.4614</v>
       </c>
       <c r="H3" t="n">
-        <v>0.7784</v>
+        <v>-1.1023</v>
       </c>
       <c r="I3" t="n">
-        <v>2.4231</v>
+        <v>3.5637</v>
       </c>
       <c r="J3" t="n">
-        <v>3.316</v>
+        <v>0.9307</v>
       </c>
       <c r="K3" t="n">
-        <v>0.648</v>
+        <v>-1.9512</v>
       </c>
       <c r="L3" t="n">
-        <v>2.668</v>
+        <v>2.882</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.1145</v>
+        <v>1.5307</v>
       </c>
       <c r="N3" t="n">
-        <v>0.1304</v>
+        <v>0.849</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.2449</v>
+        <v>0.6817</v>
       </c>
       <c r="P3" t="n">
-        <v>1.0406</v>
+        <v>-0.4162</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.0406</v>
+        <v>-2.0812</v>
       </c>
       <c r="R3" t="n">
-        <v>2.0812</v>
+        <v>1.6649</v>
       </c>
       <c r="S3" t="n">
-        <v>-2.0153</v>
+        <v>0.3473</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.64</v>
+        <v>0.8058</v>
       </c>
       <c r="U3" t="n">
-        <v>-1.3752</v>
+        <v>-0.4586</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>0.4599</v>
       </c>
       <c r="W3" t="n">
-        <v>2.565</v>
+        <v>1.6275</v>
       </c>
       <c r="X3" t="n">
-        <v>-2.565</v>
+        <v>-1.1675</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.1956</v>
+        <v>2.095</v>
       </c>
       <c r="E4" t="n">
-        <v>0.7595</v>
+        <v>0.7176</v>
       </c>
       <c r="F4" t="n">
-        <v>1.4361</v>
+        <v>1.3774</v>
       </c>
       <c r="G4" t="n">
         <v>0.427</v>
@@ -766,13 +766,13 @@
         <v>2.9137</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.2349</v>
+        <v>-0.3355</v>
       </c>
       <c r="T4" t="n">
-        <v>0.6582</v>
+        <v>0.6163</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.8931</v>
+        <v>-0.9518</v>
       </c>
       <c r="V4" t="n">
         <v>1.1711</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>R. SANTOS JIMENEZ</t>
+          <t>G. CLARKE</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.8629</v>
+        <v>1.7854</v>
       </c>
       <c r="E5" t="n">
-        <v>1.5323</v>
+        <v>3.2879</v>
       </c>
       <c r="F5" t="n">
-        <v>0.3305</v>
+        <v>-1.5025</v>
       </c>
       <c r="G5" t="n">
-        <v>0.8869</v>
+        <v>3.1474</v>
       </c>
       <c r="H5" t="n">
-        <v>2.1662</v>
+        <v>4.4773</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.2793</v>
+        <v>-1.33</v>
       </c>
       <c r="J5" t="n">
-        <v>1.0665</v>
+        <v>3.3393</v>
       </c>
       <c r="K5" t="n">
-        <v>1.7417</v>
+        <v>4.1019</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.6752</v>
+        <v>-0.7625</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.1797</v>
+        <v>-0.1919</v>
       </c>
       <c r="N5" t="n">
-        <v>0.4245</v>
+        <v>0.3755</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.6041</v>
+        <v>-0.5674</v>
       </c>
       <c r="P5" t="n">
-        <v>0.8325</v>
+        <v>1.6649</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0.8325</v>
+        <v>1.6649</v>
       </c>
       <c r="S5" t="n">
-        <v>0.1435</v>
+        <v>-0.8193</v>
       </c>
       <c r="T5" t="n">
-        <v>0.4658</v>
+        <v>-0.0514</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.3223</v>
+        <v>-0.7678</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>-2.2077</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-2.2077</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>G. CLARKE</t>
+          <t>R. SANTOS JIMENEZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.155</v>
+        <v>1.5376</v>
       </c>
       <c r="E6" t="n">
-        <v>2.6869</v>
+        <v>1.3833</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.5319</v>
+        <v>0.1544</v>
       </c>
       <c r="G6" t="n">
-        <v>3.1474</v>
+        <v>0.8869</v>
       </c>
       <c r="H6" t="n">
-        <v>4.4773</v>
+        <v>2.1662</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.33</v>
+        <v>-1.2793</v>
       </c>
       <c r="J6" t="n">
-        <v>3.3393</v>
+        <v>1.0665</v>
       </c>
       <c r="K6" t="n">
-        <v>4.1019</v>
+        <v>1.7417</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.7625</v>
+        <v>-0.6752</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.1919</v>
+        <v>-0.1797</v>
       </c>
       <c r="N6" t="n">
-        <v>0.3755</v>
+        <v>0.4245</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.5674</v>
+        <v>-0.6041</v>
       </c>
       <c r="P6" t="n">
-        <v>1.6649</v>
+        <v>0.8325</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.6649</v>
+        <v>0.8325</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.4496</v>
+        <v>-0.1817</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.6524</v>
+        <v>0.3167</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.7972</v>
+        <v>-0.4984</v>
       </c>
       <c r="V6" t="n">
-        <v>-2.2077</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-2.2077</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.1429</v>
+        <v>1.504</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.3923</v>
+        <v>-1.178</v>
       </c>
       <c r="F7" t="n">
-        <v>2.5352</v>
+        <v>2.682</v>
       </c>
       <c r="G7" t="n">
         <v>0.6564</v>
@@ -1000,13 +1000,13 @@
         <v>2.7055</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.9550999999999999</v>
+        <v>-0.594</v>
       </c>
       <c r="T7" t="n">
-        <v>0.8011</v>
+        <v>1.0154</v>
       </c>
       <c r="U7" t="n">
-        <v>-1.7562</v>
+        <v>-1.6094</v>
       </c>
       <c r="V7" t="n">
         <v>0.8173</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>M. JANKOVIC</t>
+          <t>A. LATORRE SANCHEZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0988</v>
+        <v>-0.5217000000000001</v>
       </c>
       <c r="E8" t="n">
-        <v>0.2758</v>
+        <v>0.2624</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.177</v>
+        <v>-0.7841</v>
       </c>
       <c r="G8" t="n">
-        <v>0.1805</v>
+        <v>0.705</v>
       </c>
       <c r="H8" t="n">
-        <v>0.5544</v>
+        <v>0.3433</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.3739</v>
+        <v>0.3617</v>
       </c>
       <c r="J8" t="n">
-        <v>0.1479</v>
+        <v>-0.042</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.008800000000000001</v>
+        <v>-0.08119999999999999</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1568</v>
+        <v>0.0392</v>
       </c>
       <c r="M8" t="n">
-        <v>0.0325</v>
+        <v>0.747</v>
       </c>
       <c r="N8" t="n">
-        <v>0.5632</v>
+        <v>0.4245</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.5306999999999999</v>
+        <v>0.3225</v>
       </c>
       <c r="P8" t="n">
-        <v>1.6649</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.0406</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>2.7055</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>1.7595</v>
+        <v>-0.6429</v>
       </c>
       <c r="T8" t="n">
-        <v>2.2298</v>
+        <v>0.3043</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.4703</v>
+        <v>-0.9473</v>
       </c>
       <c r="V8" t="n">
-        <v>-3.5061</v>
+        <v>-0.5838</v>
       </c>
       <c r="W8" t="n">
-        <v>-1.0614</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-2.4447</v>
+        <v>-0.5838</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. LATORRE SANCHEZ</t>
+          <t>M. JANKOVIC</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.4248</v>
+        <v>-1.0403</v>
       </c>
       <c r="E9" t="n">
-        <v>0.4767</v>
+        <v>-1.0101</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.9015</v>
+        <v>-0.0302</v>
       </c>
       <c r="G9" t="n">
-        <v>0.705</v>
+        <v>0.1805</v>
       </c>
       <c r="H9" t="n">
-        <v>0.3433</v>
+        <v>0.5544</v>
       </c>
       <c r="I9" t="n">
-        <v>0.3617</v>
+        <v>-0.3739</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.042</v>
+        <v>0.1479</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.08119999999999999</v>
+        <v>-0.008800000000000001</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0392</v>
+        <v>0.1568</v>
       </c>
       <c r="M9" t="n">
-        <v>0.747</v>
+        <v>0.0325</v>
       </c>
       <c r="N9" t="n">
-        <v>0.4245</v>
+        <v>0.5632</v>
       </c>
       <c r="O9" t="n">
-        <v>0.3225</v>
+        <v>-0.5306999999999999</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>1.6649</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-1.0406</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>2.7055</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.5461</v>
+        <v>0.6204</v>
       </c>
       <c r="T9" t="n">
-        <v>0.5185999999999999</v>
+        <v>0.944</v>
       </c>
       <c r="U9" t="n">
-        <v>-1.0647</v>
+        <v>-0.3235</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.5838</v>
+        <v>-3.5061</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>-1.0614</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.5838</v>
+        <v>-2.4447</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.6008</v>
+        <v>-2.0523</v>
       </c>
       <c r="E10" t="n">
-        <v>0.8984</v>
+        <v>0.535</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.4992</v>
+        <v>-2.5872</v>
       </c>
       <c r="G10" t="n">
         <v>-0.1341</v>
@@ -1234,13 +1234,13 @@
         <v>1.2487</v>
       </c>
       <c r="S10" t="n">
-        <v>0.3171</v>
+        <v>-0.1344</v>
       </c>
       <c r="T10" t="n">
-        <v>0.9068000000000001</v>
+        <v>0.5434</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.5898</v>
+        <v>-0.6778</v>
       </c>
       <c r="V10" t="n">
         <v>-1.9919</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.019</v>
+        <v>-2.4679</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.2776</v>
+        <v>-3.4623</v>
       </c>
       <c r="F11" t="n">
-        <v>1.2586</v>
+        <v>0.9943</v>
       </c>
       <c r="G11" t="n">
         <v>-1.0397</v>
@@ -1312,13 +1312,13 @@
         <v>2.9137</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.524</v>
+        <v>-0.9729</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.1214</v>
+        <v>0.6939</v>
       </c>
       <c r="U11" t="n">
-        <v>-1.4026</v>
+        <v>-1.6668</v>
       </c>
       <c r="V11" t="n">
         <v>-1.2878</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>7.075600000000001</v>
+        <v>7.401699999999998</v>
       </c>
       <c r="E12" t="n">
-        <v>6.764400000000002</v>
+        <v>7.090599999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>0.3109999999999999</v>
+        <v>0.3110999999999997</v>
       </c>
       <c r="G12" t="n">
         <v>10.4924</v>
@@ -1369,13 +1369,13 @@
         <v>8.493499999999999</v>
       </c>
       <c r="L12" t="n">
-        <v>0.1429000000000009</v>
+        <v>0.1429000000000005</v>
       </c>
       <c r="M12" t="n">
         <v>1.8561</v>
       </c>
       <c r="N12" t="n">
-        <v>3.958299999999999</v>
+        <v>3.9583</v>
       </c>
       <c r="O12" t="n">
         <v>-2.1022</v>
@@ -1390,13 +1390,13 @@
         <v>18.7306</v>
       </c>
       <c r="S12" t="n">
-        <v>-3.5719</v>
+        <v>-3.2457</v>
       </c>
       <c r="T12" t="n">
-        <v>5.2938</v>
+        <v>5.6199</v>
       </c>
       <c r="U12" t="n">
-        <v>-8.8657</v>
+        <v>-8.865600000000001</v>
       </c>
       <c r="V12" t="n">
         <v>-7.129</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>5.4204</v>
+        <v>4.3361</v>
       </c>
       <c r="E13" t="n">
-        <v>4.3016</v>
+        <v>3.0157</v>
       </c>
       <c r="F13" t="n">
-        <v>1.1188</v>
+        <v>1.3204</v>
       </c>
       <c r="G13" t="n">
         <v>-0.7517</v>
@@ -1468,13 +1468,13 @@
         <v>1.8731</v>
       </c>
       <c r="S13" t="n">
-        <v>2.7538</v>
+        <v>1.6695</v>
       </c>
       <c r="T13" t="n">
-        <v>3.671</v>
+        <v>2.3851</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.9172</v>
+        <v>-0.7156</v>
       </c>
       <c r="V13" t="n">
         <v>3.6264</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.3983</v>
+        <v>3.4236</v>
       </c>
       <c r="E14" t="n">
-        <v>4.9071</v>
+        <v>4.0498</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.5088</v>
+        <v>-0.6263</v>
       </c>
       <c r="G14" t="n">
         <v>0.0479</v>
@@ -1546,13 +1546,13 @@
         <v>1.4568</v>
       </c>
       <c r="S14" t="n">
-        <v>1.8072</v>
+        <v>0.8325</v>
       </c>
       <c r="T14" t="n">
-        <v>1.8417</v>
+        <v>0.9844000000000001</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.0345</v>
+        <v>-0.152</v>
       </c>
       <c r="V14" t="n">
         <v>2.3351</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.5734</v>
+        <v>3.0672</v>
       </c>
       <c r="E15" t="n">
-        <v>3.1888</v>
+        <v>4.3675</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.6154</v>
+        <v>-1.3003</v>
       </c>
       <c r="G15" t="n">
         <v>4.4732</v>
@@ -1624,13 +1624,13 @@
         <v>1.8731</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.3192</v>
+        <v>0.1747</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.1743</v>
+        <v>1.0045</v>
       </c>
       <c r="U15" t="n">
-        <v>-1.1449</v>
+        <v>-0.8298</v>
       </c>
       <c r="V15" t="n">
         <v>-0.1238</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-1.4306</v>
+        <v>-0.3718</v>
       </c>
       <c r="E16" t="n">
-        <v>-1.7254</v>
+        <v>-0.8682</v>
       </c>
       <c r="F16" t="n">
-        <v>0.2948</v>
+        <v>0.4964</v>
       </c>
       <c r="G16" t="n">
         <v>-1.0468</v>
@@ -1702,13 +1702,13 @@
         <v>1.4568</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.2996</v>
+        <v>-0.2407</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.7705</v>
+        <v>0.0867</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.5291</v>
+        <v>-0.3275</v>
       </c>
       <c r="V16" t="n">
         <v>0.7076</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>P. MARTIN MARTIN</t>
+          <t>J. HANNA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-2.0425</v>
+        <v>-1.5074</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.676</v>
+        <v>-1.2637</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.3665</v>
+        <v>-0.2437</v>
       </c>
       <c r="G17" t="n">
-        <v>-2.5266</v>
+        <v>-2.7055</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.533</v>
+        <v>-1.8825</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.9936</v>
+        <v>-0.823</v>
       </c>
       <c r="J17" t="n">
-        <v>-2.008</v>
+        <v>-1.9786</v>
       </c>
       <c r="K17" t="n">
-        <v>-1.3328</v>
+        <v>-1.2944</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.6752</v>
+        <v>-0.6842</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.5185999999999999</v>
+        <v>-0.7269</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.2002</v>
+        <v>-0.5881</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.3184</v>
+        <v>-0.1388</v>
       </c>
       <c r="P17" t="n">
-        <v>-1.4568</v>
+        <v>-1.0406</v>
       </c>
       <c r="Q17" t="n">
         <v>-2.0812</v>
       </c>
       <c r="R17" t="n">
-        <v>0.6244</v>
+        <v>1.0406</v>
       </c>
       <c r="S17" t="n">
-        <v>1.9409</v>
+        <v>0.1336</v>
       </c>
       <c r="T17" t="n">
-        <v>2.4132</v>
+        <v>0.461</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.4723</v>
+        <v>-0.3275</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>2.1051</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>2.3351</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-0.23</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. HANNA</t>
+          <t>P. MARTIN MARTIN</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.1733</v>
+        <v>-2.776</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.5852</v>
+        <v>-2.6404</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.5881999999999999</v>
+        <v>-0.1356</v>
       </c>
       <c r="G18" t="n">
-        <v>-2.7055</v>
+        <v>-2.5266</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.8825</v>
+        <v>-1.533</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.823</v>
+        <v>-0.9936</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.9786</v>
+        <v>-2.008</v>
       </c>
       <c r="K18" t="n">
-        <v>-1.2944</v>
+        <v>-1.3328</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.6842</v>
+        <v>-0.6752</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.7269</v>
+        <v>-0.5185999999999999</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.5881</v>
+        <v>-0.2002</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.1388</v>
+        <v>-0.3184</v>
       </c>
       <c r="P18" t="n">
-        <v>-1.0406</v>
+        <v>-1.4568</v>
       </c>
       <c r="Q18" t="n">
         <v>-2.0812</v>
       </c>
       <c r="R18" t="n">
-        <v>1.0406</v>
+        <v>0.6244</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.5324</v>
+        <v>1.2074</v>
       </c>
       <c r="T18" t="n">
-        <v>0.1396</v>
+        <v>1.4488</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.6719000000000001</v>
+        <v>-0.2414</v>
       </c>
       <c r="V18" t="n">
-        <v>2.1051</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>2.3351</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-5.5786</v>
+        <v>-3.7403</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.5792</v>
+        <v>0.0282</v>
       </c>
       <c r="F19" t="n">
-        <v>-3.9995</v>
+        <v>-3.7685</v>
       </c>
       <c r="G19" t="n">
         <v>-2.1956</v>
@@ -1936,13 +1936,13 @@
         <v>1.8731</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.6962</v>
+        <v>0.142</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.6153</v>
+        <v>0.9921</v>
       </c>
       <c r="U19" t="n">
-        <v>-1.081</v>
+        <v>-0.85</v>
       </c>
       <c r="V19" t="n">
         <v>-0.23</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-7.2424</v>
+        <v>-8.078200000000001</v>
       </c>
       <c r="E20" t="n">
-        <v>-6.1429</v>
+        <v>-7.0002</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.0995</v>
+        <v>-1.078</v>
       </c>
       <c r="G20" t="n">
         <v>-5.7873</v>
@@ -2014,13 +2014,13 @@
         <v>1.2487</v>
       </c>
       <c r="S20" t="n">
-        <v>1.9174</v>
+        <v>1.0817</v>
       </c>
       <c r="T20" t="n">
-        <v>2.3603</v>
+        <v>1.5031</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.4429</v>
+        <v>-0.4214</v>
       </c>
       <c r="V20" t="n">
         <v>-1.2914</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-7.0753</v>
+        <v>-5.646799999999999</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.3111999999999995</v>
+        <v>-0.311300000000001</v>
       </c>
       <c r="F21" t="n">
-        <v>-6.7643</v>
+        <v>-5.335599999999999</v>
       </c>
       <c r="G21" t="n">
         <v>-10.4924</v>
@@ -2092,13 +2092,13 @@
         <v>11.4466</v>
       </c>
       <c r="S21" t="n">
-        <v>3.5719</v>
+        <v>5.0007</v>
       </c>
       <c r="T21" t="n">
         <v>8.8657</v>
       </c>
       <c r="U21" t="n">
-        <v>-5.2938</v>
+        <v>-3.8652</v>
       </c>
       <c r="V21" t="n">
         <v>7.129</v>
